--- a/reports/集团总公司_现金流量表_2026-02.xlsx
+++ b/reports/集团总公司_现金流量表_2026-02.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>176748000</v>
+        <v>173830346</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>353496000</v>
+        <v>348292902</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3530319</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>7045082</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1760202</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>3528725</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>885113</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>1766229</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>702473</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1407678</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>531833</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1062180</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>351074</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>702659</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>265766</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>531548</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>175808</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>351342</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>441906</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>885092</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>221534</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>442196</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>140057</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>280754</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>480392</v>
+        <v>472927</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>960784</v>
+        <v>943633</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3263040</v>
+        <v>3195217</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>6526080</v>
+        <v>6404436</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>180491432</v>
+        <v>186504575</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>108768000</v>
+        <v>107237365</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>217536000</v>
+        <v>214691349</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1174233</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2344608</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>881962</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>1767623</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>588993</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1175243</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>439655</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>881360</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>295235</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>589251</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>220565</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>441842</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>21934880</v>
+        <v>21627760</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>43869760</v>
+        <v>43213679</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>10151680</v>
+        <v>9920822</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>20303360</v>
+        <v>19846330</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>4622640</v>
+        <v>4552620</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>9245280</v>
+        <v>9110016</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>145477200</v>
+        <v>146939210</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>35014232</v>
+        <v>39565365</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>247200</v>
+        <v>244201</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>494400</v>
+        <v>487715</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2163000</v>
+        <v>2133331</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>4326000</v>
+        <v>4266726</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1318400</v>
+        <v>1290597</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2636800</v>
+        <v>2579205</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2410200</v>
+        <v>2377532</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20600000</v>
+        <v>20170084</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>41200000</v>
+        <v>40261017</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2987000</v>
+        <v>2920719</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>5974000</v>
+        <v>5854758</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14626000</v>
+        <v>14372531</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>29252000</v>
+        <v>28677517</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>535600</v>
+        <v>528528</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1071200</v>
+        <v>1056533</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>21135600</v>
+        <v>20698612</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18725400</v>
+        <v>-18321080</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4841000</v>
+        <v>4759815</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>9682000</v>
+        <v>9539521</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7725000</v>
+        <v>7566813</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>15450000</v>
+        <v>15168962</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7725000</v>
+        <v>7621562</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>15450000</v>
+        <v>15211520</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>247200</v>
+        <v>241827</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>494400</v>
+        <v>484441</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12813200</v>
+        <v>12568455</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6283000</v>
+        <v>6146391</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>12566000</v>
+        <v>12295866</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6283000</v>
+        <v>6198407</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>12566000</v>
+        <v>12403140</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1030000</v>
+        <v>1009417</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2060000</v>
+        <v>2016364</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>896100</v>
+        <v>881000</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1792200</v>
+        <v>1758137</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>128750</v>
+        <v>126232</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>257500</v>
+        <v>253060</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7441750</v>
+        <v>7282040</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5371450</v>
+        <v>5286415</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>21660282</v>
+        <v>26530700</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>21660282</v>
+        <v>26530700</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
